--- a/INSTANCES/instances_xlsx/A_MTN_5/358FL_15A_5.xlsx
+++ b/INSTANCES/instances_xlsx/A_MTN_5/358FL_15A_5.xlsx
@@ -11423,7 +11423,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -11457,7 +11457,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -11474,7 +11474,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -11491,7 +11491,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -11525,7 +11525,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -11542,7 +11542,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -11576,7 +11576,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -11593,7 +11593,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -11644,7 +11644,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -11661,7 +11661,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16">
         <v>1</v>
